--- a/student_assessment_forms/003_electrostatics_knowledge_assessment--student_assessment_forms.xlsx
+++ b/student_assessment_forms/003_electrostatics_knowledge_assessment--student_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro_1</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>What is the definition of electrostatics?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>question_1_1</t>
+          <t>What are the main topics covered in electrostatics?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1_1_answer_1</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>answer_1_1</t>
+          <t>How do electric fields interact with charged particles?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_1_2</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>question_1_2</t>
+          <t>What is the difference between static and dynamic electric fields?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_1_2_answer_1</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>answer_1_2</t>
+          <t>How do materials respond to electric fields?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_1_3</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>question_1_3</t>
+          <t>What are some common applications of electrostatics in real-world scenarios?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,41 +658,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_1_3_answer_1</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>answer_1_3</t>
+          <t>How do electric potentials interact with charged particles?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_2_1</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>question_2_1</t>
+          <t>What is the relationship between electric potential and electric field?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_2_1_answer_1</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>question_2_1_answer</t>
+          <t>How do electrostatics influence our daily lives?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +727,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_2_1_answer_2</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>question_2_1_answer_2</t>
+          <t>Can you explain the concept of electric charge?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_3_1</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>question_3_1</t>
+          <t>What are some important concepts in electrostatics that you've learned in class?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,340 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_3_1_answer_1</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>answer_3_1</t>
+          <t>Can you provide an example of how electrostatics is used in a real-world scenario?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>question_3_1_answer_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>answer_3_1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_4_1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>question_4_1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question_4_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>question_4_2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_4_2_answer_1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>answer_4_2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_5_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>question_5_1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_5_1_answer_1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>answer_5_1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_5_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>question_5_2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_5_2_answer_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>answer_5_2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_5_2_answer_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>answer_5_2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_6_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>question_6_1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_6_1_answer_1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>answer_6_1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_6_1_answer_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>answer_6_1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_7_1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>question_7_1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>question_7_1_answer_1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>answer_7_1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1121,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1149,204 +827,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_1_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>electric_fields</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Electric fields</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_1_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>electric_potentials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Electric potentials</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_1_3_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>charged_particles</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Charged particles</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_1_3_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_3_1_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>electric_devices</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Electric devices</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_1_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>electric_motors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Electric motors</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_4_2_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>power_systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Power systems</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_2_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>question_5_2_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>question_5_2_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>question_6_1_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>question_6_1_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
